--- a/eduson_academy/Case2_ABC_Analysis/Кейс 2 ABC-анализ отдела продаж.xlsx
+++ b/eduson_academy/Case2_ABC_Analysis/Кейс 2 ABC-анализ отдела продаж.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40F806E3-CDDB-4EDF-8CD9-BF7C834CE1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F911C4CA-97F9-4E98-9BA8-B9A40B9C0892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Исходные_данные" sheetId="5" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </externalReferences>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="269" r:id="rId7"/>
+    <pivotCache cacheId="358" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="81">
   <si>
     <t>Филиал</t>
   </si>
@@ -178,6 +178,24 @@
     <t>Категория АВС</t>
   </si>
   <si>
+    <t>Категория</t>
+  </si>
+  <si>
+    <t>Менеджеров</t>
+  </si>
+  <si>
+    <t>Доля выручки</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>Общая выручка</t>
   </si>
   <si>
@@ -277,18 +295,26 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;₽&quot;;[Red]\-#,##0\ &quot;₽&quot;"/>
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0&quot; ₽&quot;"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -377,8 +403,13 @@
       <color theme="0"/>
       <name val="Times New Roman"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Times New Roman"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -419,6 +450,30 @@
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -620,261 +675,304 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="6" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="6" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="6" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="5" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="5" fillId="6" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" pivotButton="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" pivotButton="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="44" fontId="4" fillId="7" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="7" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="44" fontId="5" fillId="7" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="7" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="7" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="6" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="6" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="6" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="6" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="6" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="20% — акцент3" xfId="3" builtinId="38"/>
     <cellStyle name="20% — акцент5" xfId="4" builtinId="46"/>
+    <cellStyle name="60% — акцент1" xfId="5" builtinId="32"/>
     <cellStyle name="Денежный" xfId="1" builtinId="4"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Процентный" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="55">
+  <dxfs count="60">
     <dxf>
       <font>
         <b val="0"/>
@@ -1375,6 +1473,127 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF222222"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF222222"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF222222"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF222222"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.39997558519241921"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
         <name val="Times New Roman"/>
@@ -1848,6 +2067,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFC7CE"/>
+      <color rgb="FFFFEB9C"/>
+      <color rgb="FFC6EFCE"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -6139,13 +6365,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1047750</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6691,7 +6917,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FABB95B0-5BE7-46F4-80A6-8BF043C6B7A3}" name="Сводная таблица1" cacheId="269" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FABB95B0-5BE7-46F4-80A6-8BF043C6B7A3}" name="Сводная таблица1" cacheId="358" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:D7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
@@ -6755,10 +6981,10 @@
     <dataField name="Количество по полю Менеджер" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="41">
+    <format dxfId="46">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="42">
+    <format dxfId="47">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -6769,10 +6995,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="43">
+    <format dxfId="48">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
+    <format dxfId="49">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -6783,30 +7009,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="45">
+    <format dxfId="50">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="46">
+    <format dxfId="51">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="47">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="48">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="49">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="50">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="51">
-      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
     <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
@@ -6819,6 +7026,25 @@
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
     <format dxfId="54">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="55">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="56">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="57">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="58">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="59">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -6998,34 +7224,46 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5B455796-B972-446C-805F-992EA3F410AA}" name="Таблица1" displayName="Таблица1" ref="A1:E38" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" headerRowBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5B455796-B972-446C-805F-992EA3F410AA}" name="Таблица1" displayName="Таблица1" ref="A1:E38" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44" headerRowBorderDxfId="43">
   <autoFilter ref="A1:E38" xr:uid="{5B455796-B972-446C-805F-992EA3F410AA}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E1161A7C-15FC-41DE-AE22-8117A80C1059}" name="Филиал" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{103B0580-BB6C-4C64-B035-A23CC20EFD21}" name="Менеджер" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{B6820415-1184-4110-87AC-4FAFCBEC3415}" name="Продажи" dataDxfId="35" dataCellStyle="Денежный"/>
-    <tableColumn id="4" xr3:uid="{1EF72979-B87D-4E8B-A99A-2C321978B2E6}" name="Звонки " dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{202B3C70-7394-4072-826B-DDA171817FD6}" name="Встречи" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{E1161A7C-15FC-41DE-AE22-8117A80C1059}" name="Филиал" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{103B0580-BB6C-4C64-B035-A23CC20EFD21}" name="Менеджер" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{B6820415-1184-4110-87AC-4FAFCBEC3415}" name="Продажи" dataDxfId="40" dataCellStyle="Денежный"/>
+    <tableColumn id="4" xr3:uid="{1EF72979-B87D-4E8B-A99A-2C321978B2E6}" name="Звонки " dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{202B3C70-7394-4072-826B-DDA171817FD6}" name="Встречи" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E10FA177-0214-447D-8E3E-4BB06D6B4E85}" name="Таблица2" displayName="Таблица2" ref="A1:E34" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" headerRowBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E10FA177-0214-447D-8E3E-4BB06D6B4E85}" name="Таблица2" displayName="Таблица2" ref="A1:E34" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33" headerRowBorderDxfId="32">
   <autoFilter ref="A1:E34" xr:uid="{E10FA177-0214-447D-8E3E-4BB06D6B4E85}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{59EB414D-217C-4878-8D5A-2AD4137D2C59}" name="Менеджер" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{A38E2D3F-B411-400D-B505-BB0A0756965D}" name="Продажи" dataDxfId="25" dataCellStyle="Денежный"/>
-    <tableColumn id="3" xr3:uid="{3E5692D0-FB0C-4C18-ACE6-460610500EB1}" name="Доля" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{0AC921E0-21CA-46B7-B857-34A24916422D}" name="Накопительный итог" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{A55FE3F0-B98E-4739-BD00-A86BC1DBC929}" name="Категория АВС" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{59EB414D-217C-4878-8D5A-2AD4137D2C59}" name="Менеджер" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{A38E2D3F-B411-400D-B505-BB0A0756965D}" name="Продажи" dataDxfId="30" dataCellStyle="Денежный"/>
+    <tableColumn id="3" xr3:uid="{3E5692D0-FB0C-4C18-ACE6-460610500EB1}" name="Доля" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{0AC921E0-21CA-46B7-B857-34A24916422D}" name="Накопительный итог" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{A55FE3F0-B98E-4739-BD00-A86BC1DBC929}" name="Категория АВС" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{03530D29-3C09-478C-83D6-44C52F8B3B03}" name="Таблица4" displayName="Таблица4" ref="G1:I4" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+  <autoFilter ref="G1:I4" xr:uid="{03530D29-3C09-478C-83D6-44C52F8B3B03}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{FB84EC57-9674-4BA0-A466-A59500D36271}" name="Категория" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{7F82E4AF-9C93-4725-9B7C-8A5925B03761}" name="Менеджеров" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{D0E4545E-8F4E-4E77-A9DA-763593C4F212}" name="Доля выручки" dataDxfId="22"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A8411448-8494-4694-AAD3-3D8B11D1503A}" name="Таблица3" displayName="Таблица3" ref="A9:I41" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16" headerRowBorderDxfId="15">
   <autoFilter ref="A9:I41" xr:uid="{A8411448-8494-4694-AAD3-3D8B11D1503A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:I41">
@@ -7054,7 +7292,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{A1DDB90C-291F-45DA-A3ED-8BBE3B21AE57}" name="Таблица7" displayName="Таблица7" ref="F3:I7" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="F3:I7" xr:uid="{A1DDB90C-291F-45DA-A3ED-8BBE3B21AE57}"/>
   <tableColumns count="4">
@@ -8201,43 +8439,43 @@
       <c r="D19" s="1"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="116"/>
+      <c r="A20" s="128"/>
       <c r="B20" s="2"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="116"/>
+      <c r="A21" s="128"/>
       <c r="B21" s="2"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="116"/>
+      <c r="A22" s="128"/>
       <c r="B22" s="2"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="116"/>
+      <c r="A23" s="128"/>
       <c r="B23" s="2"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="116"/>
+      <c r="A24" s="128"/>
       <c r="B24" s="2"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="116"/>
+      <c r="A25" s="128"/>
       <c r="B25" s="2"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="116"/>
+      <c r="A26" s="128"/>
       <c r="B26" s="2"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -8255,55 +8493,55 @@
       <c r="D28" s="1"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="116"/>
+      <c r="A29" s="128"/>
       <c r="B29" s="2"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="116"/>
+      <c r="A30" s="128"/>
       <c r="B30" s="2"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="116"/>
+      <c r="A31" s="128"/>
       <c r="B31" s="2"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="116"/>
+      <c r="A32" s="128"/>
       <c r="B32" s="2"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="116"/>
+      <c r="A33" s="128"/>
       <c r="B33" s="2"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="116"/>
+      <c r="A34" s="128"/>
       <c r="B34" s="2"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="116"/>
+      <c r="A35" s="128"/>
       <c r="B35" s="2"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="116"/>
+      <c r="A36" s="128"/>
       <c r="B36" s="2"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="116"/>
+      <c r="A37" s="128"/>
       <c r="B37" s="2"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -8325,7 +8563,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9457AC-A9AB-4C1A-8636-1ED7FC8B7BE8}">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.140625" bestFit="1" customWidth="1"/>
@@ -8333,9 +8571,12 @@
     <col min="3" max="3" width="10.42578125" customWidth="1"/>
     <col min="4" max="4" width="25.85546875" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21.75" customHeight="1">
+    <row r="1" spans="1:13" ht="21.75" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
@@ -8351,8 +8592,21 @@
       <c r="E1" s="11" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="G1" s="121" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="121" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="121" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="58" t="s">
         <v>25</v>
       </c>
@@ -8371,8 +8625,23 @@
         <f>IF(D2&lt;=0.8,"A",IF(D2&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="G2" s="124" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="122">
+        <f>COUNTIF($E$2:$E$33,"A")</f>
+        <v>19</v>
+      </c>
+      <c r="I2" s="127">
+        <f>SUMIF($E$2:$E$33,"A",$C$2:$C$33)</f>
+        <v>0.77959331875896987</v>
+      </c>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="58" t="s">
         <v>19</v>
       </c>
@@ -8380,7 +8649,7 @@
         <v>380585</v>
       </c>
       <c r="C3" s="60">
-        <f t="shared" ref="C3:C33" si="0">B3/$B$34</f>
+        <f>B3/$B$34</f>
         <v>5.24435943880662E-2</v>
       </c>
       <c r="D3" s="61">
@@ -8391,8 +8660,23 @@
         <f>IF(D3&lt;=0.8,"A",IF(D3&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="G3" s="125" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="122">
+        <f>COUNTIF($E$2:$E$33,"B")</f>
+        <v>8</v>
+      </c>
+      <c r="I3" s="127">
+        <f>SUMIF($E$2:$E$33,"B",$C$2:$C$33)</f>
+        <v>0.15949819726651449</v>
+      </c>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="58" t="s">
         <v>30</v>
       </c>
@@ -8400,19 +8684,34 @@
         <v>379470</v>
       </c>
       <c r="C4" s="60">
-        <f t="shared" si="0"/>
+        <f>B4/$B$34</f>
         <v>5.228995037229392E-2</v>
       </c>
       <c r="D4" s="61">
-        <f t="shared" ref="D4:D33" si="1">C4+D3</f>
+        <f>C4+D3</f>
         <v>0.15904635984255278</v>
       </c>
       <c r="E4" s="62" t="str">
-        <f t="shared" ref="E3:E33" si="2">IF(D4&lt;=0.8,"A",IF(D4&lt;=0.95,"B","C"))</f>
+        <f>IF(D4&lt;=0.8,"A",IF(D4&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="G4" s="126" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="122">
+        <f>COUNTIF($E$2:$E$33,"C")</f>
+        <v>5</v>
+      </c>
+      <c r="I4" s="127">
+        <f>SUMIF($E$2:$E$33,"C",$C$2:$C$33)</f>
+        <v>6.0908483974515766E-2</v>
+      </c>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="58" t="s">
         <v>36</v>
       </c>
@@ -8420,19 +8719,19 @@
         <v>378880</v>
       </c>
       <c r="C5" s="60">
-        <f t="shared" si="0"/>
+        <f>B5/$B$34</f>
         <v>5.2208649951391996E-2</v>
       </c>
       <c r="D5" s="61">
-        <f t="shared" si="1"/>
+        <f>C5+D4</f>
         <v>0.21125500979394476</v>
       </c>
       <c r="E5" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D5&lt;=0.8,"A",IF(D5&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:13">
       <c r="A6" s="58" t="s">
         <v>14</v>
       </c>
@@ -8440,39 +8739,39 @@
         <v>373865</v>
       </c>
       <c r="C6" s="60">
-        <f t="shared" si="0"/>
+        <f>B6/$B$34</f>
         <v>5.1517596373725633E-2</v>
       </c>
       <c r="D6" s="61">
-        <f t="shared" si="1"/>
+        <f>C6+D5</f>
         <v>0.2627726061676704</v>
       </c>
       <c r="E6" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D6&lt;=0.8,"A",IF(D6&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="58" t="s">
+    <row r="7" spans="1:13">
+      <c r="A7" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="59">
+      <c r="B7" s="117">
         <v>364200</v>
       </c>
-      <c r="C7" s="60">
-        <f t="shared" si="0"/>
+      <c r="C7" s="118">
+        <f>B7/$B$34</f>
         <v>5.0185785241493253E-2</v>
       </c>
-      <c r="D7" s="61">
-        <f t="shared" si="1"/>
+      <c r="D7" s="119">
+        <f>C7+D6</f>
         <v>0.31295839140916365</v>
       </c>
-      <c r="E7" s="62" t="str">
-        <f t="shared" si="2"/>
+      <c r="E7" s="123" t="str">
+        <f>IF(D7&lt;=0.8,"A",IF(D7&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:13">
       <c r="A8" s="58" t="s">
         <v>29</v>
       </c>
@@ -8480,19 +8779,19 @@
         <v>355580</v>
       </c>
       <c r="C8" s="60">
-        <f t="shared" si="0"/>
+        <f>B8/$B$34</f>
         <v>4.8997972312383779E-2</v>
       </c>
       <c r="D8" s="61">
-        <f t="shared" si="1"/>
+        <f>C8+D7</f>
         <v>0.36195636372154744</v>
       </c>
       <c r="E8" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D8&lt;=0.8,"A",IF(D8&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:13">
       <c r="A9" s="58" t="s">
         <v>15</v>
       </c>
@@ -8500,19 +8799,19 @@
         <v>343360</v>
       </c>
       <c r="C9" s="60">
-        <f t="shared" si="0"/>
+        <f>B9/$B$34</f>
         <v>4.7314089018448996E-2</v>
       </c>
       <c r="D9" s="61">
-        <f t="shared" si="1"/>
+        <f>C9+D8</f>
         <v>0.4092704527399964</v>
       </c>
       <c r="E9" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D9&lt;=0.8,"A",IF(D9&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:13">
       <c r="A10" s="58" t="s">
         <v>24</v>
       </c>
@@ -8520,19 +8819,19 @@
         <v>302080</v>
       </c>
       <c r="C10" s="60">
-        <f t="shared" si="0"/>
+        <f>B10/$B$34</f>
         <v>4.1625815501785506E-2</v>
       </c>
       <c r="D10" s="61">
-        <f t="shared" si="1"/>
+        <f>C10+D9</f>
         <v>0.45089626824178192</v>
       </c>
       <c r="E10" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D10&lt;=0.8,"A",IF(D10&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:13">
       <c r="A11" s="58" t="s">
         <v>34</v>
       </c>
@@ -8540,19 +8839,19 @@
         <v>300895</v>
       </c>
       <c r="C11" s="60">
-        <f t="shared" si="0"/>
+        <f>B11/$B$34</f>
         <v>4.1462525673363844E-2</v>
       </c>
       <c r="D11" s="61">
-        <f t="shared" si="1"/>
+        <f>C11+D10</f>
         <v>0.49235879391514575</v>
       </c>
       <c r="E11" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D11&lt;=0.8,"A",IF(D11&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:13">
       <c r="A12" s="58" t="s">
         <v>26</v>
       </c>
@@ -8560,19 +8859,19 @@
         <v>279740</v>
       </c>
       <c r="C12" s="60">
-        <f t="shared" si="0"/>
+        <f>B12/$B$34</f>
         <v>3.8547423293397373E-2</v>
       </c>
       <c r="D12" s="61">
-        <f t="shared" si="1"/>
+        <f>C12+D11</f>
         <v>0.53090621720854314</v>
       </c>
       <c r="E12" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D12&lt;=0.8,"A",IF(D12&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:13">
       <c r="A13" s="58" t="s">
         <v>33</v>
       </c>
@@ -8580,19 +8879,19 @@
         <v>250560</v>
       </c>
       <c r="C13" s="60">
-        <f t="shared" si="0"/>
+        <f>B13/$B$34</f>
         <v>3.452649739184116E-2</v>
       </c>
       <c r="D13" s="61">
-        <f t="shared" si="1"/>
+        <f>C13+D12</f>
         <v>0.56543271460038436</v>
       </c>
       <c r="E13" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D13&lt;=0.8,"A",IF(D13&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:13">
       <c r="A14" s="58" t="s">
         <v>18</v>
       </c>
@@ -8600,39 +8899,39 @@
         <v>237800</v>
       </c>
       <c r="C14" s="60">
-        <f t="shared" si="0"/>
+        <f>B14/$B$34</f>
         <v>3.2768203543182578E-2</v>
       </c>
       <c r="D14" s="61">
-        <f t="shared" si="1"/>
+        <f>C14+D13</f>
         <v>0.59820091814356691</v>
       </c>
       <c r="E14" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D14&lt;=0.8,"A",IF(D14&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="58" t="s">
+    <row r="15" spans="1:13">
+      <c r="A15" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="59">
+      <c r="B15" s="117">
         <v>236550</v>
       </c>
-      <c r="C15" s="60">
-        <f t="shared" si="0"/>
+      <c r="C15" s="118">
+        <f>B15/$B$34</f>
         <v>3.2595956888729349E-2</v>
       </c>
-      <c r="D15" s="61">
-        <f t="shared" si="1"/>
+      <c r="D15" s="119">
+        <f>C15+D14</f>
         <v>0.63079687503229631</v>
       </c>
-      <c r="E15" s="62" t="str">
-        <f t="shared" si="2"/>
+      <c r="E15" s="120" t="str">
+        <f>IF(D15&lt;=0.8,"A",IF(D15&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:13">
       <c r="A16" s="58" t="s">
         <v>13</v>
       </c>
@@ -8640,15 +8939,15 @@
         <v>228379</v>
       </c>
       <c r="C16" s="60">
-        <f t="shared" si="0"/>
+        <f>B16/$B$34</f>
         <v>3.1470014957899473E-2</v>
       </c>
       <c r="D16" s="61">
-        <f t="shared" si="1"/>
+        <f>C16+D15</f>
         <v>0.66226688999019578</v>
       </c>
       <c r="E16" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D16&lt;=0.8,"A",IF(D16&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
     </row>
@@ -8660,15 +8959,15 @@
         <v>226899</v>
       </c>
       <c r="C17" s="60">
-        <f t="shared" si="0"/>
+        <f>B17/$B$34</f>
         <v>3.1266074919026846E-2</v>
       </c>
       <c r="D17" s="61">
-        <f t="shared" si="1"/>
+        <f>C17+D16</f>
         <v>0.69353296490922267</v>
       </c>
       <c r="E17" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D17&lt;=0.8,"A",IF(D17&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
     </row>
@@ -8680,15 +8979,15 @@
         <v>216149</v>
       </c>
       <c r="C18" s="60">
-        <f t="shared" si="0"/>
+        <f>B18/$B$34</f>
         <v>2.9784753690729065E-2</v>
       </c>
       <c r="D18" s="61">
-        <f t="shared" si="1"/>
+        <f>C18+D17</f>
         <v>0.72331771859995175</v>
       </c>
       <c r="E18" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D18&lt;=0.8,"A",IF(D18&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
     </row>
@@ -8700,15 +8999,15 @@
         <v>205348</v>
       </c>
       <c r="C19" s="60">
-        <f t="shared" si="0"/>
+        <f>B19/$B$34</f>
         <v>2.829640479892959E-2</v>
       </c>
       <c r="D19" s="61">
-        <f t="shared" si="1"/>
+        <f>C19+D18</f>
         <v>0.75161412339888134</v>
       </c>
       <c r="E19" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D19&lt;=0.8,"A",IF(D19&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
     </row>
@@ -8720,15 +9019,15 @@
         <v>203046</v>
       </c>
       <c r="C20" s="65">
-        <f t="shared" si="0"/>
+        <f>B20/$B$34</f>
         <v>2.797919536008852E-2</v>
       </c>
       <c r="D20" s="66">
-        <f t="shared" si="1"/>
+        <f>C20+D19</f>
         <v>0.77959331875896987</v>
       </c>
       <c r="E20" s="67" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D20&lt;=0.8,"A",IF(D20&lt;=0.95,"B","C"))</f>
         <v>A</v>
       </c>
     </row>
@@ -8740,15 +9039,15 @@
         <v>197900</v>
       </c>
       <c r="C21" s="60">
-        <f t="shared" si="0"/>
+        <f>B21/$B$34</f>
         <v>2.7270090333035461E-2</v>
       </c>
       <c r="D21" s="61">
-        <f t="shared" si="1"/>
+        <f>C21+D20</f>
         <v>0.80686340909200538</v>
       </c>
       <c r="E21" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D21&lt;=0.8,"A",IF(D21&lt;=0.95,"B","C"))</f>
         <v>B</v>
       </c>
     </row>
@@ -8760,15 +9059,15 @@
         <v>175230</v>
       </c>
       <c r="C22" s="60">
-        <f t="shared" si="0"/>
+        <f>B22/$B$34</f>
         <v>2.4146225007871672E-2</v>
       </c>
       <c r="D22" s="61">
-        <f t="shared" si="1"/>
+        <f>C22+D21</f>
         <v>0.83100963409987705</v>
       </c>
       <c r="E22" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D22&lt;=0.8,"A",IF(D22&lt;=0.95,"B","C"))</f>
         <v>B</v>
       </c>
     </row>
@@ -8780,15 +9079,15 @@
         <v>166480</v>
       </c>
       <c r="C23" s="60">
-        <f t="shared" si="0"/>
+        <f>B23/$B$34</f>
         <v>2.2940498426699058E-2</v>
       </c>
       <c r="D23" s="61">
-        <f t="shared" si="1"/>
+        <f>C23+D22</f>
         <v>0.85395013252657614</v>
       </c>
       <c r="E23" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D23&lt;=0.8,"A",IF(D23&lt;=0.95,"B","C"))</f>
         <v>B</v>
       </c>
     </row>
@@ -8800,15 +9099,15 @@
         <v>165500</v>
       </c>
       <c r="C24" s="60">
-        <f t="shared" si="0"/>
+        <f>B24/$B$34</f>
         <v>2.2805457049607725E-2</v>
       </c>
       <c r="D24" s="61">
-        <f t="shared" si="1"/>
+        <f>C24+D23</f>
         <v>0.87675558957618382</v>
       </c>
       <c r="E24" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D24&lt;=0.8,"A",IF(D24&lt;=0.95,"B","C"))</f>
         <v>B</v>
       </c>
     </row>
@@ -8820,15 +9119,15 @@
         <v>137579</v>
       </c>
       <c r="C25" s="60">
-        <f t="shared" si="0"/>
+        <f>B25/$B$34</f>
         <v>1.8958017978416807E-2</v>
       </c>
       <c r="D25" s="61">
-        <f t="shared" si="1"/>
+        <f>C25+D24</f>
         <v>0.89571360755460061</v>
       </c>
       <c r="E25" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D25&lt;=0.8,"A",IF(D25&lt;=0.95,"B","C"))</f>
         <v>B</v>
       </c>
     </row>
@@ -8840,15 +9139,15 @@
         <v>109200</v>
       </c>
       <c r="C26" s="60">
-        <f t="shared" si="0"/>
+        <f>B26/$B$34</f>
         <v>1.5047467733034222E-2</v>
       </c>
       <c r="D26" s="61">
-        <f t="shared" si="1"/>
+        <f>C26+D25</f>
         <v>0.91076107528763484</v>
       </c>
       <c r="E26" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D26&lt;=0.8,"A",IF(D26&lt;=0.95,"B","C"))</f>
         <v>B</v>
       </c>
     </row>
@@ -8860,15 +9159,15 @@
         <v>104950</v>
       </c>
       <c r="C27" s="60">
-        <f t="shared" si="0"/>
+        <f>B27/$B$34</f>
         <v>1.4461829107893237E-2</v>
       </c>
       <c r="D27" s="61">
-        <f t="shared" si="1"/>
+        <f>C27+D26</f>
         <v>0.92522290439552812</v>
       </c>
       <c r="E27" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D27&lt;=0.8,"A",IF(D27&lt;=0.95,"B","C"))</f>
         <v>B</v>
       </c>
     </row>
@@ -8880,15 +9179,15 @@
         <v>100645</v>
       </c>
       <c r="C28" s="65">
-        <f t="shared" si="0"/>
+        <f>B28/$B$34</f>
         <v>1.3868611629956311E-2</v>
       </c>
       <c r="D28" s="66">
-        <f t="shared" si="1"/>
+        <f>C28+D27</f>
         <v>0.93909151602548446</v>
       </c>
       <c r="E28" s="67" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D28&lt;=0.8,"A",IF(D28&lt;=0.95,"B","C"))</f>
         <v>B</v>
       </c>
     </row>
@@ -8900,15 +9199,15 @@
         <v>97400</v>
       </c>
       <c r="C29" s="60">
-        <f t="shared" si="0"/>
+        <f>B29/$B$34</f>
         <v>1.3421459314995724E-2</v>
       </c>
       <c r="D29" s="61">
-        <f t="shared" si="1"/>
+        <f>C29+D28</f>
         <v>0.95251297534048018</v>
       </c>
       <c r="E29" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D29&lt;=0.8,"A",IF(D29&lt;=0.95,"B","C"))</f>
         <v>C</v>
       </c>
     </row>
@@ -8920,15 +9219,15 @@
         <v>92000</v>
       </c>
       <c r="C30" s="60">
-        <f t="shared" si="0"/>
+        <f>B30/$B$34</f>
         <v>1.2677353767757769E-2</v>
       </c>
       <c r="D30" s="61">
-        <f t="shared" si="1"/>
+        <f>C30+D29</f>
         <v>0.96519032910823799</v>
       </c>
       <c r="E30" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D30&lt;=0.8,"A",IF(D30&lt;=0.95,"B","C"))</f>
         <v>C</v>
       </c>
     </row>
@@ -8940,15 +9239,15 @@
         <v>88510</v>
       </c>
       <c r="C31" s="60">
-        <f t="shared" si="0"/>
+        <f>B31/$B$34</f>
         <v>1.219644110852435E-2</v>
       </c>
       <c r="D31" s="61">
-        <f t="shared" si="1"/>
+        <f>C31+D30</f>
         <v>0.97738677021676235</v>
       </c>
       <c r="E31" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D31&lt;=0.8,"A",IF(D31&lt;=0.95,"B","C"))</f>
         <v>C</v>
       </c>
     </row>
@@ -8960,15 +9259,15 @@
         <v>83305</v>
       </c>
       <c r="C32" s="60">
-        <f t="shared" si="0"/>
+        <f>B32/$B$34</f>
         <v>1.1479206039381098E-2</v>
       </c>
       <c r="D32" s="61">
-        <f t="shared" si="1"/>
+        <f>C32+D31</f>
         <v>0.98886597625614348</v>
       </c>
       <c r="E32" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D32&lt;=0.8,"A",IF(D32&lt;=0.95,"B","C"))</f>
         <v>C</v>
       </c>
     </row>
@@ -8980,21 +9279,21 @@
         <v>80800</v>
       </c>
       <c r="C33" s="60">
-        <f t="shared" si="0"/>
+        <f>B33/$B$34</f>
         <v>1.1134023743856823E-2</v>
       </c>
       <c r="D33" s="61">
-        <f t="shared" si="1"/>
+        <f>C33+D32</f>
         <v>1.0000000000000002</v>
       </c>
       <c r="E33" s="62" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(D33&lt;=0.8,"A",IF(D33&lt;=0.95,"B","C"))</f>
         <v>C</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="21.75" customHeight="1">
       <c r="A34" s="57" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B34" s="68">
         <f>SUM(B2:B33)</f>
@@ -9013,23 +9312,24 @@
     <sortCondition descending="1" ref="B2:B38"/>
   </sortState>
   <conditionalFormatting sqref="E2:E20">
-    <cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="A">
+    <cfRule type="containsText" dxfId="37" priority="3" operator="containsText" text="A">
       <formula>NOT(ISERROR(SEARCH("A",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E28">
-    <cfRule type="containsText" dxfId="31" priority="2" operator="containsText" text="B">
+    <cfRule type="containsText" dxfId="36" priority="2" operator="containsText" text="B">
       <formula>NOT(ISERROR(SEARCH("B",E21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29:E33">
-    <cfRule type="containsText" dxfId="30" priority="1" operator="containsText" text="C">
+    <cfRule type="containsText" dxfId="35" priority="1" operator="containsText" text="C">
       <formula>NOT(ISERROR(SEARCH("C",E29)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9049,29 +9349,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A1" s="118" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="118"/>
+      <c r="A1" s="130" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="130"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="117" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="117"/>
+      <c r="D1" s="129" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="129"/>
     </row>
     <row r="2" spans="1:9" ht="36.75" customHeight="1">
       <c r="A2" s="30" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="28" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -9083,7 +9383,7 @@
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="19" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E3" s="20">
         <v>300000</v>
@@ -9098,7 +9398,7 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="19" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E4" s="21">
         <v>60</v>
@@ -9113,7 +9413,7 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="19" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E5" s="22">
         <v>0.02</v>
@@ -9128,35 +9428,35 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="48" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E6" s="21">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="120"/>
-      <c r="B7" s="120"/>
-      <c r="C7" s="120"/>
+      <c r="A7" s="132"/>
+      <c r="B7" s="132"/>
+      <c r="C7" s="132"/>
       <c r="D7" s="17" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E7" s="26">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="25.5" customHeight="1">
-      <c r="A8" s="119" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
+      <c r="A8" s="131" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="131"/>
+      <c r="C8" s="131"/>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="131"/>
+      <c r="G8" s="131"/>
+      <c r="H8" s="131"/>
+      <c r="I8" s="131"/>
     </row>
     <row r="9" spans="1:9" ht="36" customHeight="1">
       <c r="A9" s="31" t="s">
@@ -9175,16 +9475,16 @@
         <v>4</v>
       </c>
       <c r="F9" s="42" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="I9" s="31" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="17.25" customHeight="1">
@@ -9717,7 +10017,7 @@
     </row>
     <row r="26" spans="1:9" ht="17.25" customHeight="1">
       <c r="A26" s="70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B26" s="32" t="s">
         <v>19</v>
@@ -9750,7 +10050,7 @@
     </row>
     <row r="27" spans="1:9" ht="17.25" customHeight="1">
       <c r="A27" s="70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B27" s="32" t="s">
         <v>14</v>
@@ -9783,7 +10083,7 @@
     </row>
     <row r="28" spans="1:9" ht="17.25" customHeight="1">
       <c r="A28" s="70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B28" s="32" t="s">
         <v>15</v>
@@ -9816,7 +10116,7 @@
     </row>
     <row r="29" spans="1:9" ht="17.25" customHeight="1">
       <c r="A29" s="70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B29" s="32" t="s">
         <v>18</v>
@@ -9849,7 +10149,7 @@
     </row>
     <row r="30" spans="1:9" ht="17.25" customHeight="1">
       <c r="A30" s="70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B30" s="32" t="s">
         <v>13</v>
@@ -9882,7 +10182,7 @@
     </row>
     <row r="31" spans="1:9" ht="17.25" customHeight="1">
       <c r="A31" s="70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B31" s="32" t="s">
         <v>17</v>
@@ -9915,7 +10215,7 @@
     </row>
     <row r="32" spans="1:9" ht="17.25" customHeight="1">
       <c r="A32" s="70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B32" s="44" t="s">
         <v>11</v>
@@ -9948,7 +10248,7 @@
     </row>
     <row r="33" spans="1:9" ht="17.25" customHeight="1">
       <c r="A33" s="70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B33" s="51" t="s">
         <v>20</v>
@@ -9981,7 +10281,7 @@
     </row>
     <row r="34" spans="1:9" ht="17.25" customHeight="1">
       <c r="A34" s="70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B34" s="51" t="s">
         <v>10</v>
@@ -10014,7 +10314,7 @@
     </row>
     <row r="35" spans="1:9" ht="17.25" customHeight="1">
       <c r="A35" s="70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B35" s="51" t="s">
         <v>7</v>
@@ -10047,7 +10347,7 @@
     </row>
     <row r="36" spans="1:9" ht="17.25" customHeight="1">
       <c r="A36" s="70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B36" s="51" t="s">
         <v>12</v>
@@ -10080,7 +10380,7 @@
     </row>
     <row r="37" spans="1:9" ht="17.25" customHeight="1">
       <c r="A37" s="70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B37" s="51" t="s">
         <v>9</v>
@@ -10113,7 +10413,7 @@
     </row>
     <row r="38" spans="1:9" ht="17.25" customHeight="1">
       <c r="A38" s="70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B38" s="51" t="s">
         <v>21</v>
@@ -10146,7 +10446,7 @@
     </row>
     <row r="39" spans="1:9" ht="17.25" customHeight="1">
       <c r="A39" s="70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B39" s="51" t="s">
         <v>8</v>
@@ -10179,7 +10479,7 @@
     </row>
     <row r="40" spans="1:9" ht="17.25" customHeight="1">
       <c r="A40" s="70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B40" s="51" t="s">
         <v>6</v>
@@ -10212,7 +10512,7 @@
     </row>
     <row r="41" spans="1:9" ht="17.25" customHeight="1">
       <c r="A41" s="70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B41" s="51" t="s">
         <v>16</v>
@@ -10597,13 +10897,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E678D115-75E8-4D3B-ACF9-ABB5E34DADE8}">
-  <dimension ref="A2:K67"/>
+  <dimension ref="A2:M67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="15.85546875" customWidth="1"/>
     <col min="9" max="9" width="18.42578125" customWidth="1"/>
-    <col min="10" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="13" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="18" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -10622,47 +10924,50 @@
     <col min="34" max="34" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" ht="22.5" customHeight="1">
+    <row r="2" spans="1:13" ht="22.5" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="121" t="s">
-        <v>62</v>
-      </c>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-    </row>
-    <row r="3" spans="1:11" ht="21" customHeight="1">
+      <c r="F2" s="133" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+    </row>
+    <row r="3" spans="1:13" ht="21" customHeight="1">
       <c r="A3" s="92" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="97" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="97" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H3" s="97" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I3" s="98" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>74</v>
+      </c>
+      <c r="K3" s="135"/>
+      <c r="L3" s="136"/>
+      <c r="M3" s="134"/>
+    </row>
+    <row r="4" spans="1:13" ht="15.75">
       <c r="A4" s="93" t="s">
         <v>31</v>
       </c>
@@ -10691,8 +10996,11 @@
         <f>G4/D4</f>
         <v>0.33333333333333331</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="K4" s="135"/>
+      <c r="L4" s="137"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" ht="15.75">
       <c r="A5" s="93" t="s">
         <v>23</v>
       </c>
@@ -10721,10 +11029,13 @@
         <f t="shared" ref="I5:I6" si="0">G5/D5</f>
         <v>0.5714285714285714</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="K5" s="135"/>
+      <c r="L5" s="137"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="93" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B6" s="94">
         <v>3140615</v>
@@ -10751,10 +11062,12 @@
         <f t="shared" si="0"/>
         <v>0.1875</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="K6" s="138"/>
+      <c r="L6" s="138"/>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="93" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B7" s="94">
         <v>7257035</v>
@@ -10777,22 +11090,22 @@
         <v>0.3125</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="30.75" customHeight="1">
+    <row r="8" spans="1:13" ht="30.75" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1">
+    <row r="9" spans="1:13" ht="15" customHeight="1">
       <c r="A9" s="88" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="K9" s="83"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" s="89" t="s">
         <v>1</v>
       </c>
@@ -10803,13 +11116,13 @@
         <v>0</v>
       </c>
       <c r="D10" s="89" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F10" s="86"/>
       <c r="G10" s="87"/>
       <c r="H10" s="91"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
@@ -10826,7 +11139,7 @@
       <c r="G11" s="73"/>
       <c r="H11" s="74"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:13">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -10834,7 +11147,7 @@
         <v>380585</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D12" s="90">
         <v>300000</v>
@@ -10843,7 +11156,7 @@
       <c r="G12" s="73"/>
       <c r="H12" s="74"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:13">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
@@ -10860,7 +11173,7 @@
       <c r="G13" s="73"/>
       <c r="H13" s="74"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:13">
       <c r="A14" s="1" t="s">
         <v>36</v>
       </c>
@@ -10878,7 +11191,7 @@
       <c r="G14" s="73"/>
       <c r="H14" s="74"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:13">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -10886,7 +11199,7 @@
         <v>373865</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D15" s="90">
         <v>300000</v>
@@ -10896,7 +11209,7 @@
       <c r="G15" s="73"/>
       <c r="H15" s="74"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:13">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
@@ -10940,7 +11253,7 @@
         <v>343360</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D18" s="90">
         <v>300000</v>
@@ -11158,7 +11471,7 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="89" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="85"/>
@@ -11170,7 +11483,7 @@
     </row>
     <row r="39" spans="1:8" ht="30">
       <c r="A39" s="48" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B39" s="1">
         <f>COUNTIF(KPI_и_Оценка!$F$10:$F$41,"Да")</f>
@@ -11185,7 +11498,7 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B40" s="1">
         <f>COUNTIF(KPI_и_Оценка!$F$10:$F$41,"Нет")</f>
